--- a/output_excel/hosp4_resultados.xlsx
+++ b/output_excel/hosp4_resultados.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flopes\Documents\GitHub\Doutorado-real-datasets\output_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="SVM" sheetId="1" r:id="rId1"/>
-    <sheet name="GB" sheetId="2" r:id="rId2"/>
-    <sheet name="RF" sheetId="3" r:id="rId3"/>
+    <sheet name="(a) Gradient Boosting" sheetId="2" r:id="rId1"/>
+    <sheet name="(b) Random Forest" sheetId="3" r:id="rId2"/>
+    <sheet name="(c) Support Vector Machine" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -72,8 +77,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +141,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -180,9 +193,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -214,9 +227,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,11 +438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,145 +486,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7499044433827043</v>
+        <v>0.70949195731804426</v>
       </c>
       <c r="C2">
-        <v>0.09830695350005633</v>
+        <v>6.9633312714888651E-2</v>
       </c>
       <c r="D2">
-        <v>0.7400860009555661</v>
+        <v>0.65667701863354044</v>
       </c>
       <c r="E2">
-        <v>0.0642588786978064</v>
+        <v>7.54797815939654E-2</v>
       </c>
       <c r="F2">
-        <v>0.7195891065456282</v>
+        <v>0.64158106386367253</v>
       </c>
       <c r="G2">
-        <v>0.08047939079107602</v>
+        <v>0.1409075872060887</v>
       </c>
       <c r="H2">
-        <v>0.7301282051282051</v>
+        <v>0.71222726548813498</v>
       </c>
       <c r="I2">
-        <v>0.09624492925651941</v>
+        <v>4.3227210856686973E-2</v>
       </c>
       <c r="J2">
-        <v>0.717347507564899</v>
+        <v>0.658337314859054</v>
       </c>
       <c r="K2">
-        <v>0.07310124920022024</v>
+        <v>0.1054701190240515</v>
       </c>
       <c r="L2">
-        <v>0.7154841535276318</v>
+        <v>0.64538541168975949</v>
       </c>
       <c r="M2">
-        <v>0.07081077228394017</v>
+        <v>0.1150345088802823</v>
       </c>
       <c r="N2">
-        <v>0.7105988214683867</v>
+        <v>0.73145007166746301</v>
       </c>
       <c r="O2">
-        <v>0.07926458688899007</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.2015899486108739E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6549450549450549</v>
+        <v>0.62527472527472516</v>
       </c>
       <c r="C3">
-        <v>0.1215267367116418</v>
+        <v>0.1225163844586262</v>
       </c>
       <c r="D3">
-        <v>0.6395604395604396</v>
+        <v>0.61318681318681312</v>
       </c>
       <c r="E3">
-        <v>0.07509604203635117</v>
+        <v>0.15080390784372771</v>
       </c>
       <c r="F3">
-        <v>0.7032967032967032</v>
+        <v>0.49120879120879118</v>
       </c>
       <c r="G3">
-        <v>0.09767246612434714</v>
+        <v>7.2435839550228559E-2</v>
       </c>
       <c r="H3">
-        <v>0.7043956043956043</v>
+        <v>0.58021978021978027</v>
       </c>
       <c r="I3">
-        <v>0.09230115099795039</v>
+        <v>9.369702746062511E-2</v>
       </c>
       <c r="J3">
-        <v>0.6857142857142857</v>
+        <v>0.58351648351648355</v>
       </c>
       <c r="K3">
-        <v>0.1161928781352642</v>
+        <v>0.1068536530772109</v>
       </c>
       <c r="L3">
-        <v>0.6109890109890109</v>
+        <v>0.55054945054945048</v>
       </c>
       <c r="M3">
-        <v>0.06620822123688823</v>
+        <v>6.5520682135225716E-2</v>
       </c>
       <c r="N3">
-        <v>0.6098901098901098</v>
+        <v>0.58131868131868136</v>
       </c>
       <c r="O3">
-        <v>0.1071076301627359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>7.1681715416705233E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.7126811594202899</v>
+        <v>0.70217391304347831</v>
       </c>
       <c r="C4">
-        <v>0.155441750122544</v>
+        <v>0.16979576795236909</v>
       </c>
       <c r="D4">
-        <v>0.6692028985507246</v>
+        <v>0.6851449275362318</v>
       </c>
       <c r="E4">
-        <v>0.1349096526076977</v>
+        <v>0.16217765275246751</v>
       </c>
       <c r="F4">
-        <v>0.6945652173913043</v>
+        <v>0.78876811594202889</v>
       </c>
       <c r="G4">
-        <v>0.1324670582789945</v>
+        <v>0.16863207876266509</v>
       </c>
       <c r="H4">
-        <v>0.6692028985507246</v>
+        <v>0.67753623188405798</v>
       </c>
       <c r="I4">
-        <v>0.178272283716109</v>
+        <v>7.7677052806225874E-2</v>
       </c>
       <c r="J4">
-        <v>0.6094202898550725</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="K4">
-        <v>0.1388477937522512</v>
+        <v>0.19261174221426741</v>
       </c>
       <c r="L4">
-        <v>0.6351449275362319</v>
+        <v>0.67753623188405798</v>
       </c>
       <c r="M4">
-        <v>0.1384868682814744</v>
+        <v>0.15949746978916349</v>
       </c>
       <c r="N4">
-        <v>0.661231884057971</v>
+        <v>0.68550724637681171</v>
       </c>
       <c r="O4">
-        <v>0.1421957206752928</v>
+        <v>9.0892575617909893E-2</v>
       </c>
     </row>
   </sheetData>
@@ -618,11 +633,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,145 +681,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7094919573180443</v>
+        <v>0.71576286032807768</v>
       </c>
       <c r="C2">
-        <v>0.06963331271488865</v>
+        <v>1.2394392683805079E-2</v>
       </c>
       <c r="D2">
-        <v>0.6566770186335404</v>
+        <v>0.71239648033126302</v>
       </c>
       <c r="E2">
-        <v>0.0754797815939654</v>
+        <v>3.2301546371336483E-2</v>
       </c>
       <c r="F2">
-        <v>0.6415810638636725</v>
+        <v>0.69264612199394793</v>
       </c>
       <c r="G2">
-        <v>0.1409075872060887</v>
+        <v>9.7738779945590507E-2</v>
       </c>
       <c r="H2">
-        <v>0.712227265488135</v>
+        <v>0.72698080904602647</v>
       </c>
       <c r="I2">
-        <v>0.04322721085668697</v>
+        <v>2.376184131948832E-2</v>
       </c>
       <c r="J2">
-        <v>0.658337314859054</v>
+        <v>0.71327838827838819</v>
       </c>
       <c r="K2">
-        <v>0.1054701190240515</v>
+        <v>2.5737925464639971E-2</v>
       </c>
       <c r="L2">
-        <v>0.6453854116897595</v>
+        <v>0.71602165949992036</v>
       </c>
       <c r="M2">
-        <v>0.1150345088802823</v>
+        <v>3.2113779913462558E-2</v>
       </c>
       <c r="N2">
-        <v>0.731450071667463</v>
+        <v>0.74284917980570153</v>
       </c>
       <c r="O2">
-        <v>0.02201589948610874</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>3.3556215155876791E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6252747252747252</v>
+        <v>0.62747252747252746</v>
       </c>
       <c r="C3">
-        <v>0.1225163844586262</v>
+        <v>0.1174848110848712</v>
       </c>
       <c r="D3">
-        <v>0.6131868131868131</v>
+        <v>0.61208791208791202</v>
       </c>
       <c r="E3">
-        <v>0.1508039078437277</v>
+        <v>9.7641552223865807E-2</v>
       </c>
       <c r="F3">
-        <v>0.4912087912087912</v>
+        <v>0.55274725274725278</v>
       </c>
       <c r="G3">
-        <v>0.07243583955022856</v>
+        <v>0.14006140078844839</v>
       </c>
       <c r="H3">
-        <v>0.5802197802197803</v>
+        <v>0.64175824175824181</v>
       </c>
       <c r="I3">
-        <v>0.09369702746062511</v>
+        <v>9.7238777167599766E-2</v>
       </c>
       <c r="J3">
-        <v>0.5835164835164836</v>
+        <v>0.62637362637362626</v>
       </c>
       <c r="K3">
-        <v>0.1068536530772109</v>
+        <v>7.5736531604891341E-2</v>
       </c>
       <c r="L3">
-        <v>0.5505494505494505</v>
+        <v>0.61208791208791202</v>
       </c>
       <c r="M3">
-        <v>0.06552068213522572</v>
+        <v>9.3374267192298924E-2</v>
       </c>
       <c r="N3">
-        <v>0.5813186813186814</v>
+        <v>0.61098901098901093</v>
       </c>
       <c r="O3">
-        <v>0.07168171541670523</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>8.8032198169210124E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.7021739130434783</v>
+        <v>0.68478260869565222</v>
       </c>
       <c r="C4">
-        <v>0.1697957679523691</v>
+        <v>0.16307869989930801</v>
       </c>
       <c r="D4">
-        <v>0.6851449275362318</v>
+        <v>0.6681159420289855</v>
       </c>
       <c r="E4">
-        <v>0.1621776527524675</v>
+        <v>0.1584673843043381</v>
       </c>
       <c r="F4">
-        <v>0.7887681159420289</v>
+        <v>0.7195652173913043</v>
       </c>
       <c r="G4">
-        <v>0.1686320787626651</v>
+        <v>0.18463780202712579</v>
       </c>
       <c r="H4">
-        <v>0.677536231884058</v>
+        <v>0.70181159420289863</v>
       </c>
       <c r="I4">
-        <v>0.07767705280622587</v>
+        <v>0.14024126299435119</v>
       </c>
       <c r="J4">
-        <v>0.6333333333333334</v>
+        <v>0.65942028985507251</v>
       </c>
       <c r="K4">
-        <v>0.1926117422142674</v>
+        <v>0.16388670837534269</v>
       </c>
       <c r="L4">
-        <v>0.677536231884058</v>
+        <v>0.64275362318840579</v>
       </c>
       <c r="M4">
-        <v>0.1594974697891635</v>
+        <v>0.14189189442615721</v>
       </c>
       <c r="N4">
-        <v>0.6855072463768117</v>
+        <v>0.71956521739130441</v>
       </c>
       <c r="O4">
-        <v>0.09089257561790989</v>
+        <v>0.1113091597691727</v>
       </c>
     </row>
   </sheetData>
@@ -813,11 +828,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,145 +876,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7157628603280777</v>
+        <v>0.74990444338270434</v>
       </c>
       <c r="C2">
-        <v>0.01239439268380508</v>
+        <v>9.8306953500056332E-2</v>
       </c>
       <c r="D2">
-        <v>0.712396480331263</v>
+        <v>0.74008600095556609</v>
       </c>
       <c r="E2">
-        <v>0.03230154637133648</v>
+        <v>6.4258878697806401E-2</v>
       </c>
       <c r="F2">
-        <v>0.6926461219939479</v>
+        <v>0.71958910654562824</v>
       </c>
       <c r="G2">
-        <v>0.09773877994559051</v>
+        <v>8.0479390791076022E-2</v>
       </c>
       <c r="H2">
-        <v>0.7269808090460265</v>
+        <v>0.73012820512820509</v>
       </c>
       <c r="I2">
-        <v>0.02376184131948832</v>
+        <v>9.624492925651941E-2</v>
       </c>
       <c r="J2">
-        <v>0.7132783882783882</v>
+        <v>0.71734750756489896</v>
       </c>
       <c r="K2">
-        <v>0.02573792546463997</v>
+        <v>7.3101249200220236E-2</v>
       </c>
       <c r="L2">
-        <v>0.7160216594999204</v>
+        <v>0.71548415352763184</v>
       </c>
       <c r="M2">
-        <v>0.03211377991346256</v>
+        <v>7.0810772283940171E-2</v>
       </c>
       <c r="N2">
-        <v>0.7428491798057015</v>
+        <v>0.71059882146838671</v>
       </c>
       <c r="O2">
-        <v>0.03355621515587679</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>7.9264586888990074E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6274725274725275</v>
+        <v>0.65494505494505495</v>
       </c>
       <c r="C3">
-        <v>0.1174848110848712</v>
+        <v>0.1215267367116418</v>
       </c>
       <c r="D3">
-        <v>0.612087912087912</v>
+        <v>0.63956043956043962</v>
       </c>
       <c r="E3">
-        <v>0.09764155222386581</v>
+        <v>7.5096042036351174E-2</v>
       </c>
       <c r="F3">
-        <v>0.5527472527472528</v>
+        <v>0.70329670329670324</v>
       </c>
       <c r="G3">
-        <v>0.1400614007884484</v>
+        <v>9.7672466124347143E-2</v>
       </c>
       <c r="H3">
-        <v>0.6417582417582418</v>
+        <v>0.70439560439560434</v>
       </c>
       <c r="I3">
-        <v>0.09723877716759977</v>
+        <v>9.2301150997950387E-2</v>
       </c>
       <c r="J3">
-        <v>0.6263736263736263</v>
+        <v>0.68571428571428572</v>
       </c>
       <c r="K3">
-        <v>0.07573653160489134</v>
+        <v>0.1161928781352642</v>
       </c>
       <c r="L3">
-        <v>0.612087912087912</v>
+        <v>0.61098901098901093</v>
       </c>
       <c r="M3">
-        <v>0.09337426719229892</v>
+        <v>6.6208221236888229E-2</v>
       </c>
       <c r="N3">
-        <v>0.6109890109890109</v>
+        <v>0.60989010989010983</v>
       </c>
       <c r="O3">
-        <v>0.08803219816921012</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>0.1071076301627359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6847826086956522</v>
+        <v>0.71268115942028987</v>
       </c>
       <c r="C4">
-        <v>0.163078699899308</v>
+        <v>0.15544175012254399</v>
       </c>
       <c r="D4">
-        <v>0.6681159420289855</v>
+        <v>0.66920289855072457</v>
       </c>
       <c r="E4">
-        <v>0.1584673843043381</v>
+        <v>0.13490965260769769</v>
       </c>
       <c r="F4">
-        <v>0.7195652173913043</v>
+        <v>0.69456521739130428</v>
       </c>
       <c r="G4">
-        <v>0.1846378020271258</v>
+        <v>0.13246705827899449</v>
       </c>
       <c r="H4">
-        <v>0.7018115942028986</v>
+        <v>0.66920289855072457</v>
       </c>
       <c r="I4">
-        <v>0.1402412629943512</v>
+        <v>0.17827228371610901</v>
       </c>
       <c r="J4">
-        <v>0.6594202898550725</v>
+        <v>0.60942028985507246</v>
       </c>
       <c r="K4">
-        <v>0.1638867083753427</v>
+        <v>0.1388477937522512</v>
       </c>
       <c r="L4">
-        <v>0.6427536231884058</v>
+        <v>0.63514492753623186</v>
       </c>
       <c r="M4">
-        <v>0.1418918944261572</v>
+        <v>0.13848686828147441</v>
       </c>
       <c r="N4">
-        <v>0.7195652173913044</v>
+        <v>0.66123188405797095</v>
       </c>
       <c r="O4">
-        <v>0.1113091597691727</v>
+        <v>0.14219572067529279</v>
       </c>
     </row>
   </sheetData>
